--- a/data/trans_orig/P1423-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1423-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de depresión o ansiedad en 2007</t>
+          <t>Población con diagnóstico de depresión o ansiedad en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>6595</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20488</t>
+          <t>21283</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>7039</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20646</t>
+          <t>20630</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489314</t>
+          <t>489221</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>447001</t>
+          <t>446206</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>461013</t>
+          <t>460894</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>940907</t>
+          <t>940923</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>954557</t>
+          <t>954514</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8327</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21948</t>
+          <t>23623</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14328</t>
+          <t>14281</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33165</t>
+          <t>33744</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26272</t>
+          <t>25148</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48947</t>
+          <t>48590</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>713541</t>
+          <t>711866</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>727162</t>
+          <t>727250</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>592329</t>
+          <t>591750</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>611166</t>
+          <t>611213</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1312035</t>
+          <t>1312392</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1334710</t>
+          <t>1335834</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11753</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29229</t>
+          <t>30297</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28810</t>
+          <t>29083</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53826</t>
+          <t>53292</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45629</t>
+          <t>44772</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75833</t>
+          <t>75505</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>609439</t>
+          <t>608371</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>626915</t>
+          <t>627101</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>635918</t>
+          <t>636452</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660934</t>
+          <t>660661</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1252579</t>
+          <t>1252907</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1282783</t>
+          <t>1283640</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,63%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9261</t>
+          <t>9418</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25782</t>
+          <t>25516</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44700</t>
+          <t>44383</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72162</t>
+          <t>73506</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58081</t>
+          <t>58567</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90540</t>
+          <t>91602</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>493365</t>
+          <t>493631</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>509886</t>
+          <t>509729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>443480</t>
+          <t>442136</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>470942</t>
+          <t>471259</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>944249</t>
+          <t>943187</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>976708</t>
+          <t>976222</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14013</t>
+          <t>13871</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31153</t>
+          <t>31226</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38961</t>
+          <t>38868</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67399</t>
+          <t>65658</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>59257</t>
+          <t>58930</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91011</t>
+          <t>91181</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>355557</t>
+          <t>355484</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>372697</t>
+          <t>372839</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>336587</t>
+          <t>338328</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>365025</t>
+          <t>365118</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>699685</t>
+          <t>699515</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>731439</t>
+          <t>731766</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,55%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9354</t>
+          <t>9290</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23549</t>
+          <t>23010</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29828</t>
+          <t>29941</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>51965</t>
+          <t>52601</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43507</t>
+          <t>43568</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70403</t>
+          <t>69468</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>269034</t>
+          <t>269573</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>283229</t>
+          <t>283293</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>290969</t>
+          <t>290333</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>313106</t>
+          <t>312993</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>565114</t>
+          <t>566049</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>592010</t>
+          <t>591949</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,14%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8996</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22815</t>
+          <t>23609</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22887</t>
+          <t>22456</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45431</t>
+          <t>45425</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34958</t>
+          <t>35369</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>62656</t>
+          <t>63437</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>187068</t>
+          <t>186274</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>200887</t>
+          <t>201152</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>288477</t>
+          <t>288483</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>311021</t>
+          <t>311452</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>481135</t>
+          <t>480354</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>508833</t>
+          <t>508422</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,5%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>82495</t>
+          <t>82672</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>121211</t>
+          <t>122507</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>226831</t>
+          <t>226997</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>288464</t>
+          <t>288276</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>324573</t>
+          <t>326547</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>398476</t>
+          <t>396959</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3155332</t>
+          <t>3154036</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3194048</t>
+          <t>3193871</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3090733</t>
+          <t>3090921</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3152366</t>
+          <t>3152200</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6257265</t>
+          <t>6258782</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6331168</t>
+          <t>6329194</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de depresión o ansiedad en 2012</t>
+          <t>Población con diagnóstico de depresión o ansiedad en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2686</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13982</t>
+          <t>13645</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5129</t>
+          <t>4844</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19412</t>
+          <t>18885</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>445036</t>
+          <t>444919</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453153</t>
+          <t>453104</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>416248</t>
+          <t>416585</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>427544</t>
+          <t>427602</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>864964</t>
+          <t>865491</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>879247</t>
+          <t>879532</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12790</t>
+          <t>12988</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31168</t>
+          <t>32654</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17229</t>
+          <t>16792</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>37911</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33645</t>
+          <t>34885</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>63834</t>
+          <t>66123</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>655919</t>
+          <t>654433</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>674297</t>
+          <t>674099</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>571263</t>
+          <t>572344</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>593026</t>
+          <t>593463</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1233508</t>
+          <t>1231219</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1263697</t>
+          <t>1262457</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>16867</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39068</t>
+          <t>39734</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54250</t>
+          <t>54844</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>85886</t>
+          <t>87019</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76207</t>
+          <t>77911</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115035</t>
+          <t>117054</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>642795</t>
+          <t>642129</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>665229</t>
+          <t>664996</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>623688</t>
+          <t>622555</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>655324</t>
+          <t>654730</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1276402</t>
+          <t>1274383</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1315230</t>
+          <t>1313526</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>18127</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40273</t>
+          <t>39151</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61625</t>
+          <t>60753</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95887</t>
+          <t>95672</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84457</t>
+          <t>85980</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>128428</t>
+          <t>123683</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>574344</t>
+          <t>575466</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>596209</t>
+          <t>596490</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>518377</t>
+          <t>518592</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>552639</t>
+          <t>553511</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1100452</t>
+          <t>1105197</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1144423</t>
+          <t>1142900</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,0%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22420</t>
+          <t>21369</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43429</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65953</t>
+          <t>66996</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>100921</t>
+          <t>100684</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>94803</t>
+          <t>95116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>135555</t>
+          <t>134531</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>385978</t>
+          <t>386000</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>407009</t>
+          <t>408060</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>346879</t>
+          <t>347116</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>381847</t>
+          <t>380804</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>741674</t>
+          <t>742698</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>782426</t>
+          <t>782113</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,16%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9241</t>
+          <t>9365</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27402</t>
+          <t>27350</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54865</t>
+          <t>54757</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>83874</t>
+          <t>84945</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67372</t>
+          <t>68654</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>103751</t>
+          <t>103151</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>282384</t>
+          <t>282436</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>300545</t>
+          <t>300421</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>270122</t>
+          <t>269051</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>299131</t>
+          <t>299239</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>560031</t>
+          <t>560631</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>596410</t>
+          <t>595128</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,66%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9477</t>
+          <t>9410</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27877</t>
+          <t>28399</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58082</t>
+          <t>57349</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91566</t>
+          <t>90094</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73115</t>
+          <t>74420</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>110959</t>
+          <t>111809</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>221974</t>
+          <t>221452</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>240374</t>
+          <t>240441</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>297413</t>
+          <t>298885</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>330897</t>
+          <t>331630</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>527871</t>
+          <t>527021</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>565715</t>
+          <t>564410</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,35%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>119409</t>
+          <t>118968</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>169596</t>
+          <t>168850</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>364180</t>
+          <t>366728</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>441185</t>
+          <t>444837</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>504880</t>
+          <t>506773</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>599533</t>
+          <t>597587</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3257183</t>
+          <t>3257929</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3307370</t>
+          <t>3307811</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3113913</t>
+          <t>3110261</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3190918</t>
+          <t>3188370</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6382344</t>
+          <t>6384290</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6476997</t>
+          <t>6475104</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,74%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de depresión o ansiedad en 2016</t>
+          <t>Población con diagnóstico de depresión o ansiedad en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1060</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11298</t>
+          <t>9689</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21620</t>
+          <t>21771</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9471</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25779</t>
+          <t>26276</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>408165</t>
+          <t>409774</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>418403</t>
+          <t>418474</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>374135</t>
+          <t>373984</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>389120</t>
+          <t>389685</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>789439</t>
+          <t>788942</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>805747</t>
+          <t>805288</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>2968</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14783</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7782</t>
+          <t>7632</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22364</t>
+          <t>21622</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13395</t>
+          <t>13354</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30201</t>
+          <t>30821</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7124,7 +7124,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>575713</t>
+          <t>577346</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>587508</t>
+          <t>587528</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>541180</t>
+          <t>541922</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>555762</t>
+          <t>555912</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1123839</t>
+          <t>1123219</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1140645</t>
+          <t>1140686</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,7 +7232,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27141</t>
+          <t>27000</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33007</t>
+          <t>33024</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57642</t>
+          <t>59098</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47381</t>
+          <t>48089</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77030</t>
+          <t>75650</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>641956</t>
+          <t>642097</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>658943</t>
+          <t>659761</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>603744</t>
+          <t>602288</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>628379</t>
+          <t>628362</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1253453</t>
+          <t>1254833</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1283102</t>
+          <t>1282394</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17592</t>
+          <t>17528</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38454</t>
+          <t>37835</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59434</t>
+          <t>62090</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94918</t>
+          <t>95959</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85023</t>
+          <t>83025</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124966</t>
+          <t>123174</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>607594</t>
+          <t>608213</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>628456</t>
+          <t>628520</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>554159</t>
+          <t>553118</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>589643</t>
+          <t>586987</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1170159</t>
+          <t>1171951</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1210102</t>
+          <t>1212100</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21589</t>
+          <t>21736</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45266</t>
+          <t>47509</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72158</t>
+          <t>72699</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107861</t>
+          <t>107773</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>97815</t>
+          <t>99738</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>140652</t>
+          <t>141926</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>432652</t>
+          <t>430409</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>456329</t>
+          <t>456182</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>388988</t>
+          <t>389076</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>424691</t>
+          <t>424150</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>834115</t>
+          <t>832841</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>876952</t>
+          <t>875029</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,77%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>4795</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17236</t>
+          <t>16851</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>51829</t>
+          <t>50433</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>80630</t>
+          <t>81117</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60520</t>
+          <t>60000</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>95285</t>
+          <t>94022</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>317094</t>
+          <t>317479</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>329517</t>
+          <t>329535</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>297132</t>
+          <t>296645</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>325933</t>
+          <t>327329</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>616807</t>
+          <t>618070</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>651572</t>
+          <t>652092</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,57%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9740</t>
+          <t>9739</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23430</t>
+          <t>23761</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8769,7 +8769,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45842</t>
+          <t>44764</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78734</t>
+          <t>77140</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59821</t>
+          <t>60377</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>94854</t>
+          <t>95513</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>233568</t>
+          <t>233237</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>247258</t>
+          <t>247259</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>321435</t>
+          <t>323029</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>354327</t>
+          <t>355405</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>562313</t>
+          <t>561654</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>597346</t>
+          <t>596790</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,81%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>92138</t>
+          <t>91379</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>133487</t>
+          <t>132771</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>327383</t>
+          <t>323651</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>399455</t>
+          <t>398752</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>425952</t>
+          <t>434571</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>515234</t>
+          <t>519549</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3260863</t>
+          <t>3261579</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3302212</t>
+          <t>3302971</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3145087</t>
+          <t>3145790</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3217159</t>
+          <t>3220891</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6423658</t>
+          <t>6419343</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6512940</t>
+          <t>6504321</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de depresión o ansiedad en 2023</t>
+          <t>Población con diagnóstico de depresión o ansiedad en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2745</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23844</t>
+          <t>27427</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10252</t>
+          <t>9334</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34275</t>
+          <t>34990</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16354</t>
+          <t>15617</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>46821</t>
+          <t>45574</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>376143</t>
+          <t>372560</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>397242</t>
+          <t>396909</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278925</t>
+          <t>278210</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>302948</t>
+          <t>303866</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>666366</t>
+          <t>667613</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>696833</t>
+          <t>697570</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20615</t>
+          <t>20876</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18820</t>
+          <t>20002</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46930</t>
+          <t>47954</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29643</t>
+          <t>30617</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60871</t>
+          <t>62387</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>402932</t>
+          <t>402671</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>418662</t>
+          <t>418345</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>465163</t>
+          <t>464139</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>493273</t>
+          <t>492091</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>874769</t>
+          <t>873253</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>905997</t>
+          <t>905023</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22181</t>
+          <t>21896</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44323</t>
+          <t>44443</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31370</t>
+          <t>30667</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>55489</t>
+          <t>54696</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58916</t>
+          <t>58973</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91045</t>
+          <t>92559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>492015</t>
+          <t>491895</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>514157</t>
+          <t>514442</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>536513</t>
+          <t>537306</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>560632</t>
+          <t>561335</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1037295</t>
+          <t>1035781</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1069424</t>
+          <t>1069367</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,77%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20226</t>
+          <t>20928</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76148</t>
+          <t>74368</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72808</t>
+          <t>73368</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104763</t>
+          <t>104961</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80129</t>
+          <t>86257</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>172457</t>
+          <t>175844</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>811638</t>
+          <t>813418</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>867560</t>
+          <t>866858</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>608118</t>
+          <t>607920</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>640073</t>
+          <t>639513</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1428210</t>
+          <t>1424823</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1520538</t>
+          <t>1514410</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,61%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42138</t>
+          <t>41467</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68721</t>
+          <t>65389</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>82553</t>
+          <t>83639</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108383</t>
+          <t>110413</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>130981</t>
+          <t>131975</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>167623</t>
+          <t>168994</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>492513</t>
+          <t>495845</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>519096</t>
+          <t>519767</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>439522</t>
+          <t>437492</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>465352</t>
+          <t>464266</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>941516</t>
+          <t>940145</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>978158</t>
+          <t>977164</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,1%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11510</t>
+          <t>11698</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24961</t>
+          <t>25119</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25898</t>
+          <t>27367</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>100270</t>
+          <t>101406</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43220</t>
+          <t>39901</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>109018</t>
+          <t>108036</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>343204</t>
+          <t>343046</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>356655</t>
+          <t>356467</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>508098</t>
+          <t>506962</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>582470</t>
+          <t>581001</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>867515</t>
+          <t>868497</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>933313</t>
+          <t>936632</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,91%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18642</t>
+          <t>18697</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34608</t>
+          <t>33624</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57855</t>
+          <t>58909</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80170</t>
+          <t>80810</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82276</t>
+          <t>82434</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>110247</t>
+          <t>107370</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>248151</t>
+          <t>249135</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>264117</t>
+          <t>264062</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>345661</t>
+          <t>345021</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>367976</t>
+          <t>366922</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>598343</t>
+          <t>601220</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>626314</t>
+          <t>626156</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,37%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>156248</t>
+          <t>155788</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>231927</t>
+          <t>229127</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>333079</t>
+          <t>334413</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>458157</t>
+          <t>455450</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>533889</t>
+          <t>525435</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>673135</t>
+          <t>669137</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3227890</t>
+          <t>3230690</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3303569</t>
+          <t>3304029</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3254123</t>
+          <t>3256830</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3379201</t>
+          <t>3377867</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,66%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6498962</t>
+          <t>6502960</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6638208</t>
+          <t>6646662</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1423-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1423-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4843</t>
+          <t>5797</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6595</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21283</t>
+          <t>19985</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7039</t>
+          <t>6612</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20630</t>
+          <t>21669</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489221</t>
+          <t>488267</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>446206</t>
+          <t>447504</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>460894</t>
+          <t>461120</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>940923</t>
+          <t>939884</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>954514</t>
+          <t>954941</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23623</t>
+          <t>22365</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14281</t>
+          <t>14007</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33744</t>
+          <t>33438</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25148</t>
+          <t>25486</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48590</t>
+          <t>49432</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>711866</t>
+          <t>713124</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>727250</t>
+          <t>727704</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>591750</t>
+          <t>592056</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>611213</t>
+          <t>611487</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1312392</t>
+          <t>1311550</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1335834</t>
+          <t>1335496</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11567</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30297</t>
+          <t>28039</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29083</t>
+          <t>28203</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>53292</t>
+          <t>54635</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44772</t>
+          <t>45089</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75505</t>
+          <t>75407</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>608371</t>
+          <t>610629</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>627101</t>
+          <t>627373</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>636452</t>
+          <t>635109</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>660661</t>
+          <t>661541</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1252907</t>
+          <t>1253005</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1283640</t>
+          <t>1283323</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>8817</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25516</t>
+          <t>24686</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44383</t>
+          <t>44702</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73506</t>
+          <t>72776</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58567</t>
+          <t>58185</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>91602</t>
+          <t>90571</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>493631</t>
+          <t>494461</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>509729</t>
+          <t>510330</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>442136</t>
+          <t>442866</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>471259</t>
+          <t>470940</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>943187</t>
+          <t>944218</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>976222</t>
+          <t>976604</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,38%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13871</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>31226</t>
+          <t>32172</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38868</t>
+          <t>39334</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>65658</t>
+          <t>66880</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58930</t>
+          <t>58853</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>91181</t>
+          <t>90867</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>355484</t>
+          <t>354538</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>372839</t>
+          <t>372233</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>338328</t>
+          <t>337106</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>365118</t>
+          <t>364652</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>699515</t>
+          <t>699829</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>731766</t>
+          <t>731843</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>8750</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23010</t>
+          <t>23082</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29941</t>
+          <t>30211</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52601</t>
+          <t>53175</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43568</t>
+          <t>43866</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>69468</t>
+          <t>71430</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>269573</t>
+          <t>269501</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>283293</t>
+          <t>283833</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>290333</t>
+          <t>289759</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>312993</t>
+          <t>312723</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>566049</t>
+          <t>564087</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>591949</t>
+          <t>591651</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,1%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8731</t>
+          <t>8377</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23609</t>
+          <t>23062</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22456</t>
+          <t>22038</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45425</t>
+          <t>45884</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35369</t>
+          <t>34867</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63437</t>
+          <t>63509</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,68%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>186274</t>
+          <t>186821</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>201152</t>
+          <t>201506</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>288483</t>
+          <t>288024</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>311452</t>
+          <t>311870</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>480354</t>
+          <t>480282</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>508422</t>
+          <t>508924</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>82672</t>
+          <t>83266</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>122507</t>
+          <t>121468</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>226997</t>
+          <t>222029</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>288276</t>
+          <t>284522</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>326547</t>
+          <t>318267</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>396959</t>
+          <t>393864</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3154036</t>
+          <t>3155075</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3193871</t>
+          <t>3193277</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3090921</t>
+          <t>3094675</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3152200</t>
+          <t>3157168</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6258782</t>
+          <t>6261877</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6329194</t>
+          <t>6337474</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9227</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2628</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13645</t>
+          <t>14277</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>5580</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18885</t>
+          <t>18204</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>444919</t>
+          <t>444161</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>453104</t>
+          <t>453118</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>416585</t>
+          <t>415953</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>427602</t>
+          <t>427461</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>865491</t>
+          <t>866172</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>879532</t>
+          <t>878796</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12988</t>
+          <t>11833</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32654</t>
+          <t>32260</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16792</t>
+          <t>17318</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37911</t>
+          <t>38189</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34885</t>
+          <t>34720</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66123</t>
+          <t>63824</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>654433</t>
+          <t>654827</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>674099</t>
+          <t>675254</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>572344</t>
+          <t>572066</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>593463</t>
+          <t>592937</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1231219</t>
+          <t>1233518</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1262457</t>
+          <t>1262622</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16867</t>
+          <t>16516</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39734</t>
+          <t>40123</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54844</t>
+          <t>54779</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>87019</t>
+          <t>87397</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77911</t>
+          <t>77717</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>117054</t>
+          <t>117654</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>642129</t>
+          <t>641740</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>664996</t>
+          <t>665347</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>622555</t>
+          <t>622177</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>654730</t>
+          <t>654795</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1274383</t>
+          <t>1273783</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1313526</t>
+          <t>1313720</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18127</t>
+          <t>18881</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39151</t>
+          <t>39955</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60753</t>
+          <t>60765</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95672</t>
+          <t>94827</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85980</t>
+          <t>84345</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123683</t>
+          <t>125176</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>575466</t>
+          <t>574662</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>596490</t>
+          <t>595736</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>518592</t>
+          <t>519437</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>553511</t>
+          <t>553499</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1105197</t>
+          <t>1103704</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1142900</t>
+          <t>1144535</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>93,14%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21369</t>
+          <t>20592</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>43429</t>
+          <t>43119</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>66996</t>
+          <t>66908</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>100684</t>
+          <t>101103</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>95116</t>
+          <t>94320</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134531</t>
+          <t>134673</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,35%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>386000</t>
+          <t>386310</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>408060</t>
+          <t>408837</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>347116</t>
+          <t>346697</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>380804</t>
+          <t>380892</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>742698</t>
+          <t>742556</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>782113</t>
+          <t>782909</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>84,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,25%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9365</t>
+          <t>9044</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27350</t>
+          <t>27795</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54757</t>
+          <t>54803</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>84945</t>
+          <t>85413</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>68654</t>
+          <t>68634</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>103151</t>
+          <t>105472</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>282436</t>
+          <t>281991</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>300421</t>
+          <t>300742</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>269051</t>
+          <t>268583</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>299239</t>
+          <t>299193</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>560631</t>
+          <t>558310</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>595128</t>
+          <t>595148</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9410</t>
+          <t>9857</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28399</t>
+          <t>29780</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>57349</t>
+          <t>59278</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90094</t>
+          <t>90566</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74420</t>
+          <t>73441</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>111809</t>
+          <t>110748</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>221452</t>
+          <t>220071</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>240441</t>
+          <t>239994</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>298885</t>
+          <t>298413</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>331630</t>
+          <t>329701</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>527021</t>
+          <t>528082</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>564410</t>
+          <t>565389</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,5%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>118968</t>
+          <t>117403</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>168850</t>
+          <t>170544</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>366728</t>
+          <t>371315</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>444837</t>
+          <t>444017</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>506773</t>
+          <t>504603</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>597587</t>
+          <t>594476</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3257929</t>
+          <t>3256235</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3307811</t>
+          <t>3309376</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3110261</t>
+          <t>3111081</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3188370</t>
+          <t>3183783</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6384290</t>
+          <t>6387401</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6475104</t>
+          <t>6477274</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,77%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>10928</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6070</t>
+          <t>6480</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21771</t>
+          <t>20831</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9930</t>
+          <t>9573</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26276</t>
+          <t>26432</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>409774</t>
+          <t>408535</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>418474</t>
+          <t>418055</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>373984</t>
+          <t>374924</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>389685</t>
+          <t>389275</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>788942</t>
+          <t>788786</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>805288</t>
+          <t>805645</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2968</t>
+          <t>2963</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13150</t>
+          <t>13082</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>7546</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21622</t>
+          <t>22343</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13354</t>
+          <t>13521</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30821</t>
+          <t>30244</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,62%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>577346</t>
+          <t>577414</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>587528</t>
+          <t>587533</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>541922</t>
+          <t>541201</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>555912</t>
+          <t>555998</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1123219</t>
+          <t>1123796</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1140686</t>
+          <t>1140519</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9336</t>
+          <t>9244</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27000</t>
+          <t>25432</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33024</t>
+          <t>34898</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59098</t>
+          <t>58497</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>48089</t>
+          <t>46500</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>75650</t>
+          <t>76617</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>642097</t>
+          <t>643665</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>659761</t>
+          <t>659853</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>602288</t>
+          <t>602889</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>628362</t>
+          <t>626488</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1254833</t>
+          <t>1253866</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1282394</t>
+          <t>1283983</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17528</t>
+          <t>17163</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37835</t>
+          <t>37719</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62090</t>
+          <t>61214</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95959</t>
+          <t>96241</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83025</t>
+          <t>82256</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123174</t>
+          <t>123418</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>608213</t>
+          <t>608329</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>628520</t>
+          <t>628885</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>553118</t>
+          <t>552836</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>586987</t>
+          <t>587863</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1171951</t>
+          <t>1171707</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1212100</t>
+          <t>1212869</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21736</t>
+          <t>21479</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47509</t>
+          <t>44149</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72699</t>
+          <t>70774</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107773</t>
+          <t>104083</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>99738</t>
+          <t>100181</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>141926</t>
+          <t>143959</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>430409</t>
+          <t>433769</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>456182</t>
+          <t>456439</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>389076</t>
+          <t>392766</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>424150</t>
+          <t>426075</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>832841</t>
+          <t>830808</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>875029</t>
+          <t>874586</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4795</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16851</t>
+          <t>16842</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>50433</t>
+          <t>51391</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81117</t>
+          <t>81366</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>58990</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>94022</t>
+          <t>93299</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>317479</t>
+          <t>317488</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>329535</t>
+          <t>329566</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>296645</t>
+          <t>296396</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>327329</t>
+          <t>326371</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>618070</t>
+          <t>618793</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>652092</t>
+          <t>653102</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,72%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9739</t>
+          <t>9863</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23761</t>
+          <t>22752</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44764</t>
+          <t>44785</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>77140</t>
+          <t>77118</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60377</t>
+          <t>59939</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95513</t>
+          <t>94640</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>233237</t>
+          <t>234246</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>247259</t>
+          <t>247135</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>323029</t>
+          <t>323051</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>355405</t>
+          <t>355384</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>561654</t>
+          <t>562527</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>596790</t>
+          <t>597228</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,88%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>91379</t>
+          <t>91904</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>132771</t>
+          <t>132452</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>323651</t>
+          <t>323335</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>398752</t>
+          <t>399186</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>434571</t>
+          <t>434479</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>519549</t>
+          <t>521099</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,51%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3261579</t>
+          <t>3261898</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3302971</t>
+          <t>3302446</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3145790</t>
+          <t>3145356</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3220891</t>
+          <t>3221207</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6419343</t>
+          <t>6417793</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6504321</t>
+          <t>6504413</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27427</t>
+          <t>22387</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>19579</t>
+          <t>20141</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9334</t>
+          <t>10668</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34990</t>
+          <t>34576</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>28498</t>
+          <t>30449</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15617</t>
+          <t>17665</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45574</t>
+          <t>47512</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>391068</t>
+          <t>397485</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>372560</t>
+          <t>385406</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>396909</t>
+          <t>404403</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>293621</t>
+          <t>342371</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278210</t>
+          <t>327936</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>303866</t>
+          <t>351844</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>684689</t>
+          <t>739856</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>667613</t>
+          <t>722793</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>697570</t>
+          <t>752640</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10773</t>
+          <t>14565</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20876</t>
+          <t>27077</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33339</t>
+          <t>35832</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20002</t>
+          <t>25421</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47954</t>
+          <t>52342</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>44112</t>
+          <t>50397</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30617</t>
+          <t>35944</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>62387</t>
+          <t>66634</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>412774</t>
+          <t>462325</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>402671</t>
+          <t>449813</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>418345</t>
+          <t>468877</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>478754</t>
+          <t>465901</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464139</t>
+          <t>449391</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>492091</t>
+          <t>476312</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>891528</t>
+          <t>928226</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>873253</t>
+          <t>911989</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>905023</t>
+          <t>942679</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>512093</t>
+          <t>501733</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935640</t>
+          <t>978623</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>31742</t>
+          <t>33653</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21896</t>
+          <t>23321</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44443</t>
+          <t>49144</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>42465</t>
+          <t>49394</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30667</t>
+          <t>38923</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54696</t>
+          <t>60501</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>74207</t>
+          <t>83048</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58973</t>
+          <t>68247</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92559</t>
+          <t>100511</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>504596</t>
+          <t>587184</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>491895</t>
+          <t>571693</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>514442</t>
+          <t>597516</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>549537</t>
+          <t>573799</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>537306</t>
+          <t>562692</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>561335</t>
+          <t>584270</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1054133</t>
+          <t>1160981</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1035781</t>
+          <t>1143518</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1069367</t>
+          <t>1175782</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>592002</t>
+          <t>623193</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1128340</t>
+          <t>1244029</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49301</t>
+          <t>54405</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20928</t>
+          <t>41622</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74368</t>
+          <t>72151</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>89648</t>
+          <t>98542</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>73368</t>
+          <t>83304</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104961</t>
+          <t>112381</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>138949</t>
+          <t>152947</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86257</t>
+          <t>133527</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>175844</t>
+          <t>176109</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>838485</t>
+          <t>646212</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>813418</t>
+          <t>628466</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>866858</t>
+          <t>658995</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>623233</t>
+          <t>638344</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>607920</t>
+          <t>624505</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>639513</t>
+          <t>653582</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1461718</t>
+          <t>1284557</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1424823</t>
+          <t>1261395</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1514410</t>
+          <t>1303977</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>53801</t>
+          <t>55744</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41467</t>
+          <t>43310</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65389</t>
+          <t>71256</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>96299</t>
+          <t>107090</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>83639</t>
+          <t>91910</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>110413</t>
+          <t>120463</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>150100</t>
+          <t>162834</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>131975</t>
+          <t>143916</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>168994</t>
+          <t>184364</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>507433</t>
+          <t>553602</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>495845</t>
+          <t>538090</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>519767</t>
+          <t>566036</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>451606</t>
+          <t>501765</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>437492</t>
+          <t>488392</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>464266</t>
+          <t>516945</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,42%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>959039</t>
+          <t>1055368</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>940145</t>
+          <t>1033838</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>977164</t>
+          <t>1074286</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,19%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547905</t>
+          <t>608855</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1109139</t>
+          <t>1218202</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17459</t>
+          <t>18351</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11698</t>
+          <t>12251</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25119</t>
+          <t>26566</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>62958</t>
+          <t>69348</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27367</t>
+          <t>59292</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>101406</t>
+          <t>81689</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>80417</t>
+          <t>87699</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>39901</t>
+          <t>74744</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>108036</t>
+          <t>100898</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>350706</t>
+          <t>388729</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>343046</t>
+          <t>380514</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>356467</t>
+          <t>394829</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>545410</t>
+          <t>369818</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>506962</t>
+          <t>357477</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>581001</t>
+          <t>379874</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>896116</t>
+          <t>758547</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>868497</t>
+          <t>745348</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>936632</t>
+          <t>771502</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>91,17%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>25372</t>
+          <t>28022</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18697</t>
+          <t>20592</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33624</t>
+          <t>37030</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>68840</t>
+          <t>76283</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58909</t>
+          <t>64524</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80810</t>
+          <t>88498</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>94212</t>
+          <t>104304</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82434</t>
+          <t>90391</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>107370</t>
+          <t>120996</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>257387</t>
+          <t>282176</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>249135</t>
+          <t>273168</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>264062</t>
+          <t>289606</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>356991</t>
+          <t>388326</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>345021</t>
+          <t>376111</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>366922</t>
+          <t>400085</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>83,83%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>614378</t>
+          <t>670503</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>601220</t>
+          <t>653811</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>626156</t>
+          <t>684416</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>88,33%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>197367</t>
+          <t>215047</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>155788</t>
+          <t>186900</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>229127</t>
+          <t>247797</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>413127</t>
+          <t>456631</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>334413</t>
+          <t>422986</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>455450</t>
+          <t>493459</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>610494</t>
+          <t>671678</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>525435</t>
+          <t>620917</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>669137</t>
+          <t>712908</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3262450</t>
+          <t>3317715</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3230690</t>
+          <t>3284965</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3304029</t>
+          <t>3345862</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3299153</t>
+          <t>3280323</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3256830</t>
+          <t>3243495</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3377867</t>
+          <t>3313968</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6561603</t>
+          <t>6598038</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6502960</t>
+          <t>6556808</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6646662</t>
+          <t>6648799</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>91,46%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
